--- a/data/cierre.xlsx
+++ b/data/cierre.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{0A15ABEF-5FFD-4773-A3AB-628AB851EA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F0AE3AD-A377-43EA-AAE8-27B556042F6E}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{0A15ABEF-5FFD-4773-A3AB-628AB851EA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49AA7F20-A656-44EB-9A13-408587F2B38A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="175">
   <si>
     <t>Name</t>
   </si>
@@ -553,6 +553,9 @@
   </si>
   <si>
     <t>Colombia</t>
+  </si>
+  <si>
+    <t>COMPLETED</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1032,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>31</v>
@@ -1052,7 +1055,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>31</v>
@@ -1075,7 +1078,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>31</v>
@@ -1098,7 +1101,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>31</v>
@@ -1121,7 +1124,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>31</v>
@@ -1144,7 +1147,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>31</v>
@@ -1167,7 +1170,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>12</v>
+        <v>174</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>31</v>
